--- a/standardDataset/过去standardDataset.xlsx
+++ b/standardDataset/过去standardDataset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="19200" windowHeight="8080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1120,13 +1120,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="33.25" customWidth="1"/>
+    <col min="1" max="1" width="33.2545454545455" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="46.5" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="68.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="68.6272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5">
